--- a/data/trans_dic/IP1007-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos convulsivos</t>
+          <t>Menores que padecen trastornos convulsivos (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,32</t>
+          <t>0,36; 3,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,14</t>
+          <t>0,12; 1,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,56</t>
+          <t>0,06; 0,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,73</t>
+          <t>0,07; 0,78</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,81</t>
+          <t>0,08; 0,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,03</t>
+          <t>0,18; 1,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,16; 0,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,4</t>
+          <t>0,04; 0,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,55</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos convulsivos (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4268</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4080</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>636; 5932</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5234</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5860</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>551; 5477</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3229</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4428</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>553; 5944</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4881</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>627; 7450</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2150</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2851</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2894</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2911</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3051</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3696</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5006</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>524; 4717</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5008</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1286; 8022</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3485</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>628; 5923</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2284; 9260</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>570; 6710</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1157; 7500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1007-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,34</t>
+          <t>0,36; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -793,42 +793,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,15</t>
+          <t>0,12; 1,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,67</t>
+          <t>0,06; 0,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,78</t>
+          <t>0,07; 0,74</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
     </row>
@@ -1008,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,69</t>
+          <t>0,08; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,11</t>
+          <t>0,17; 1,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,66</t>
+          <t>0,17; 0,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4268</t>
+          <t>0; 4264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>0; 4129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>636; 5932</t>
+          <t>640; 6198</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1474,42 +1474,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 5702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5860</t>
+          <t>0; 6322</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>551; 5477</t>
+          <t>552; 5711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 3963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4428</t>
+          <t>0; 4296</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>553; 5944</t>
+          <t>551; 5140</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4881</t>
+          <t>0; 5424</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>627; 7450</t>
+          <t>625; 7144</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>0; 3162</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 2837</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3466</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2900</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0; 2851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2894</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2911</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3051</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>0; 4196</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>524; 4717</t>
+          <t>523; 5144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5008</t>
+          <t>0; 5484</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6255</t>
+          <t>0; 5816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1286; 8022</t>
+          <t>1259; 7484</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3485</t>
+          <t>0; 3448</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>628; 5923</t>
+          <t>624; 5837</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2284; 9260</t>
+          <t>2331; 9310</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>570; 6710</t>
+          <t>571; 6744</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1157; 7500</t>
+          <t>1158; 7525</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1007-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,34%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,49</t>
+          <t>0,36; 3,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,12; 1,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,58</t>
+          <t>0,06; 0,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,74</t>
+          <t>0,07; 0,73</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,37 +898,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,76</t>
+          <t>0,17; 1,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,71</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,81</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,8</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,83</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 1,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,46</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,78</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,66</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,46</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,05; 0,55</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1253,22 +1253,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1214</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4264</t>
+          <t>0; 4710</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4129</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>640; 6198</t>
+          <t>635; 5900</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1163</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>551; 5453</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5702</t>
+          <t>0; 3786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6322</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>552; 5711</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3963</t>
+          <t>0; 4495</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>0; 5817</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>551; 5140</t>
+          <t>553; 4975</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5424</t>
+          <t>0; 5578</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>625; 7144</t>
+          <t>627; 7054</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3162</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2837</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3466</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2900</t>
+          <t>0; 2307</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2851</t>
+          <t>0; 2864</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 3765</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1163</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>523; 5144</t>
+          <t>1257; 7408</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5484</t>
+          <t>0; 3575</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5816</t>
+          <t>622; 5324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1259; 7484</t>
+          <t>524; 5498</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3448</t>
+          <t>0; 5622</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>624; 5837</t>
+          <t>0; 5820</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2331; 9310</t>
+          <t>1935; 9296</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>571; 6744</t>
+          <t>568; 5749</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1158; 7525</t>
+          <t>696; 7921</t>
         </is>
       </c>
     </row>
